--- a/data/performance/daily/signal_list_2026-05-10.xlsx
+++ b/data/performance/daily/signal_list_2026-05-10.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 33.9%  (41W / 80L of 121 evaluated)</t>
+          <t>Win Rate: 38.8%  (47W / 74L of 121 evaluated)</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D6" t="n">
         <v>408</v>
@@ -595,10 +595,10 @@
         <v>412</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0</v>
+        <v>-0.97</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D8" t="n">
         <v>76</v>
@@ -679,10 +679,10 @@
         <v>79</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.6</v>
+        <v>3.95</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.3</v>
+        <v>0</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4660</v>
+        <v>4510</v>
       </c>
       <c r="D9" t="n">
         <v>4700</v>
@@ -721,10 +721,10 @@
         <v>4830</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.65</v>
+        <v>7.1</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.86</v>
+        <v>4.21</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1695</v>
+        <v>1690</v>
       </c>
       <c r="D12" t="n">
         <v>1660</v>
@@ -847,10 +847,10 @@
         <v>1700</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.29</v>
+        <v>0.59</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.06</v>
+        <v>-1.78</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D14" t="n">
         <v>350</v>
@@ -931,14 +931,14 @@
         <v>354</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.14</v>
+        <v>1.72</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.57</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D17" t="n">
         <v>139</v>
@@ -1057,14 +1057,14 @@
         <v>142</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.9</v>
+        <v>1.43</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-0.71</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D20" t="n">
         <v>398</v>
@@ -1183,10 +1183,10 @@
         <v>410</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.49</v>
+        <v>0.99</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.45</v>
+        <v>-1.97</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="D22" t="n">
         <v>1240</v>
@@ -1267,10 +1267,10 @@
         <v>1245</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4.62</v>
+        <v>5.06</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>4.2</v>
+        <v>4.64</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D23" t="n">
         <v>140</v>
@@ -1309,10 +1309,10 @@
         <v>147</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.08</v>
+        <v>4.26</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.78</v>
+        <v>-0.71</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D26" t="n">
         <v>188</v>
@@ -1435,10 +1435,10 @@
         <v>198</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.51</v>
+        <v>1.54</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-4.57</v>
+        <v>-3.59</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D28" t="n">
         <v>125</v>
@@ -1519,10 +1519,10 @@
         <v>129</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.57</v>
+        <v>-0.79</v>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D32" t="n">
         <v>434</v>
@@ -1687,10 +1687,10 @@
         <v>440</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.91</v>
+        <v>-1.36</v>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1490</v>
+        <v>1455</v>
       </c>
       <c r="D33" t="n">
         <v>1505</v>
@@ -1729,10 +1729,10 @@
         <v>1515</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.68</v>
+        <v>4.12</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.01</v>
+        <v>3.44</v>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D34" t="n">
         <v>118</v>
@@ -1771,10 +1771,10 @@
         <v>131</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.97</v>
+        <v>0.77</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-6.35</v>
+        <v>-9.23</v>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="D37" t="n">
         <v>340</v>
@@ -1897,10 +1897,10 @@
         <v>370</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>2.78</v>
+        <v>-7.5</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-5.56</v>
+        <v>-15</v>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D38" t="n">
         <v>127</v>
@@ -1939,10 +1939,10 @@
         <v>133</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>15.65</v>
+        <v>19.82</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>10.43</v>
+        <v>14.41</v>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1740</v>
+        <v>1750</v>
       </c>
       <c r="D39" t="n">
         <v>1740</v>
@@ -1981,10 +1981,10 @@
         <v>1755</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.86</v>
+        <v>0.29</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>0</v>
+        <v>-0.57</v>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3130</v>
+        <v>3150</v>
       </c>
       <c r="D40" t="n">
         <v>3060</v>
@@ -2023,10 +2023,10 @@
         <v>3150</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-2.24</v>
+        <v>-2.86</v>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D41" t="n">
         <v>276</v>
@@ -2065,10 +2065,10 @@
         <v>284</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>3.65</v>
+        <v>4.41</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>0.73</v>
+        <v>1.47</v>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="D42" t="n">
         <v>905</v>
@@ -2107,10 +2107,10 @@
         <v>940</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-3.72</v>
+        <v>-3.21</v>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D43" t="n">
         <v>73</v>
@@ -2149,10 +2149,10 @@
         <v>79</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>-7.59</v>
+        <v>-2.67</v>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D44" t="n">
         <v>101</v>
@@ -2191,14 +2191,14 @@
         <v>105</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1.94</v>
+        <v>5</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>-1.94</v>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>1</v>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D46" t="n">
         <v>258</v>
@@ -2275,10 +2275,10 @@
         <v>270</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>-4.44</v>
+        <v>-3.01</v>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6200</v>
+        <v>6125</v>
       </c>
       <c r="D47" t="n">
         <v>6225</v>
@@ -2317,10 +2317,10 @@
         <v>6225</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.4</v>
+        <v>1.63</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>0.4</v>
+        <v>1.63</v>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="D49" t="n">
         <v>760</v>
@@ -2401,10 +2401,10 @@
         <v>1000</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>16.28</v>
+        <v>12.36</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>-11.63</v>
+        <v>-14.61</v>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1340</v>
+        <v>1335</v>
       </c>
       <c r="D50" t="n">
         <v>1330</v>
@@ -2443,10 +2443,10 @@
         <v>1345</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.37</v>
+        <v>0.75</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-0.75</v>
+        <v>-0.37</v>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="D51" t="n">
         <v>1230</v>
@@ -2485,10 +2485,10 @@
         <v>1250</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.4</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>-1.2</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1620</v>
+        <v>1600</v>
       </c>
       <c r="D52" t="n">
         <v>1600</v>
@@ -2527,10 +2527,10 @@
         <v>1625</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.31</v>
+        <v>1.56</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-1.23</v>
+        <v>0</v>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D56" t="n">
         <v>396</v>
@@ -2695,10 +2695,10 @@
         <v>412</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2550</v>
+        <v>2530</v>
       </c>
       <c r="D58" t="n">
         <v>2600</v>
@@ -2779,10 +2779,10 @@
         <v>2900</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>13.73</v>
+        <v>14.62</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>1.96</v>
+        <v>2.77</v>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="D59" t="n">
         <v>372</v>
@@ -2821,10 +2821,10 @@
         <v>394</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>8.24</v>
+        <v>15.2</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>2.2</v>
+        <v>8.77</v>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="D60" t="n">
         <v>165</v>
@@ -2863,10 +2863,10 @@
         <v>193</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>47.33</v>
+        <v>30.41</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>25.95</v>
+        <v>11.49</v>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>855</v>
+        <v>840</v>
       </c>
       <c r="D61" t="n">
         <v>850</v>
@@ -2905,14 +2905,14 @@
         <v>885</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>3.51</v>
+        <v>5.36</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>1.19</v>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="D62" t="n">
         <v>550</v>
@@ -2947,14 +2947,14 @@
         <v>555</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>0.91</v>
+        <v>1.83</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.92</v>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D64" t="n">
         <v>99</v>
@@ -3031,10 +3031,10 @@
         <v>116</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>24.73</v>
+        <v>30.34</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>6.45</v>
+        <v>11.24</v>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1285</v>
+        <v>1295</v>
       </c>
       <c r="D66" t="n">
         <v>1290</v>
@@ -3115,14 +3115,14 @@
         <v>1295</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-0.39</v>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D67" t="n">
         <v>83</v>
@@ -3157,10 +3157,10 @@
         <v>86</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>-3.49</v>
+        <v>-2.35</v>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>8575</v>
+        <v>8600</v>
       </c>
       <c r="D70" t="n">
         <v>8700</v>
@@ -3283,10 +3283,10 @@
         <v>8750</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>2.04</v>
+        <v>1.74</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="D71" t="n">
         <v>212</v>
@@ -3325,10 +3325,10 @@
         <v>230</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>8.49</v>
+        <v>-0.86</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>0</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="D72" t="n">
         <v>384</v>
@@ -3367,10 +3367,10 @@
         <v>460</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>21.05</v>
+        <v>23.66</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>1.05</v>
+        <v>3.23</v>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="D76" t="n">
         <v>192</v>
@@ -3535,10 +3535,10 @@
         <v>206</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>19.77</v>
+        <v>10.16</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>11.63</v>
+        <v>2.67</v>
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D79" t="n">
         <v>50</v>
@@ -3661,10 +3661,10 @@
         <v>55</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>-9.09</v>
+        <v>-5.66</v>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="D81" t="n">
         <v>252</v>
@@ -3745,14 +3745,14 @@
         <v>268</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>3.08</v>
+        <v>9.84</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>-3.08</v>
-      </c>
-      <c r="H81" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>3.28</v>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D82" t="n">
         <v>81</v>
@@ -3787,14 +3787,14 @@
         <v>81</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>1.25</v>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D83" t="n">
         <v>88</v>
@@ -3829,10 +3829,10 @@
         <v>101</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>16.09</v>
+        <v>17.44</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>1.15</v>
+        <v>2.33</v>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="D84" t="n">
         <v>560</v>
@@ -3871,10 +3871,10 @@
         <v>595</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>0</v>
+        <v>-0.83</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>-5.88</v>
+        <v>-6.67</v>
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D85" t="n">
         <v>75</v>
@@ -3913,10 +3913,10 @@
         <v>78</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>-1.32</v>
+        <v>0</v>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D86" t="n">
         <v>168</v>
@@ -3955,10 +3955,10 @@
         <v>174</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>3.57</v>
+        <v>2.35</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>0</v>
+        <v>-1.18</v>
       </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D87" t="n">
         <v>228</v>
@@ -3997,10 +3997,10 @@
         <v>230</v>
       </c>
       <c r="F87" s="4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G87" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="G87" s="4" t="n">
-        <v>-0.87</v>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D89" t="n">
         <v>294</v>
@@ -4081,10 +4081,10 @@
         <v>320</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>11.11</v>
+        <v>11.89</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="H89" s="6" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D92" t="n">
         <v>95</v>
@@ -4207,14 +4207,14 @@
         <v>101</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>5.21</v>
+        <v>8.6</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="H92" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>2.15</v>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D94" t="n">
         <v>82</v>
@@ -4291,10 +4291,10 @@
         <v>83</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>7.79</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>6.49</v>
+        <v>7.89</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="D95" t="n">
         <v>426</v>
@@ -4333,10 +4333,10 @@
         <v>434</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>5.34</v>
+        <v>6.37</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>3.4</v>
+        <v>4.41</v>
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D96" t="n">
         <v>48</v>
@@ -4375,14 +4375,14 @@
         <v>48</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>9.09</v>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D97" t="n">
         <v>78</v>
@@ -4417,10 +4417,10 @@
         <v>84</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>6.33</v>
+        <v>3.7</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>-1.27</v>
+        <v>-3.7</v>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D98" t="n">
         <v>258</v>
@@ -4459,10 +4459,10 @@
         <v>310</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>2.65</v>
+        <v>4.03</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>-14.57</v>
+        <v>-13.42</v>
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="D99" t="n">
         <v>1015</v>
@@ -4501,10 +4501,10 @@
         <v>1035</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>9.52</v>
+        <v>10.11</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>7.41</v>
+        <v>7.98</v>
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D101" t="n">
         <v>97</v>
@@ -4585,10 +4585,10 @@
         <v>104</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>14.29</v>
+        <v>18.18</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>6.59</v>
+        <v>10.23</v>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="D102" t="n">
         <v>995</v>
@@ -4627,10 +4627,10 @@
         <v>1010</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1</v>
+        <v>1.51</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D103" t="n">
         <v>194</v>
@@ -4669,10 +4669,10 @@
         <v>212</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>18.44</v>
+        <v>19.77</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>8.380000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="H103" s="6" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D105" t="n">
         <v>123</v>
@@ -4753,10 +4753,10 @@
         <v>127</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>0.79</v>
+        <v>2.42</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>-2.38</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D106" t="n">
         <v>95</v>
@@ -4795,10 +4795,10 @@
         <v>98</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>4.26</v>
+        <v>5.38</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>1.06</v>
+        <v>2.15</v>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D107" t="n">
         <v>94</v>
@@ -4837,10 +4837,10 @@
         <v>100</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>16.28</v>
+        <v>19.05</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D108" t="n">
         <v>67</v>
@@ -4879,10 +4879,10 @@
         <v>68</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>6.25</v>
+        <v>4.62</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>4.69</v>
+        <v>3.08</v>
       </c>
       <c r="H108" s="6" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D109" t="n">
         <v>158</v>
@@ -4921,10 +4921,10 @@
         <v>167</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>9.869999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>3.95</v>
+        <v>4.64</v>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D110" t="n">
         <v>216</v>
@@ -4963,10 +4963,10 @@
         <v>216</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>30.91</v>
+        <v>34.16</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>30.91</v>
+        <v>34.16</v>
       </c>
       <c r="H110" s="6" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>505</v>
+        <v>488</v>
       </c>
       <c r="D111" t="n">
         <v>510</v>
@@ -5005,10 +5005,10 @@
         <v>530</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>4.95</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>0.99</v>
+        <v>4.51</v>
       </c>
       <c r="H111" s="6" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D113" t="n">
         <v>151</v>
@@ -5089,10 +5089,10 @@
         <v>194</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>27.63</v>
+        <v>28.48</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>-0.66</v>
+        <v>0</v>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D114" t="n">
         <v>121</v>
@@ -5131,10 +5131,10 @@
         <v>130</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1.56</v>
+        <v>3.17</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>-5.47</v>
+        <v>-3.97</v>
       </c>
       <c r="H114" s="5" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="D116" t="n">
         <v>240</v>
@@ -5215,14 +5215,14 @@
         <v>260</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>3.17</v>
+        <v>13.04</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>-4.76</v>
-      </c>
-      <c r="H116" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>4.35</v>
+      </c>
+      <c r="H116" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5248,7 +5248,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D117" t="n">
         <v>89</v>
@@ -5257,10 +5257,10 @@
         <v>98</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>18.07</v>
+        <v>22.5</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>7.23</v>
+        <v>11.25</v>
       </c>
       <c r="H117" s="6" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>490</v>
+        <v>466</v>
       </c>
       <c r="D118" t="n">
         <v>498</v>
@@ -5299,10 +5299,10 @@
         <v>570</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>16.33</v>
+        <v>22.32</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>1.63</v>
+        <v>6.87</v>
       </c>
       <c r="H118" s="6" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="D119" t="n">
         <v>134</v>
@@ -5341,14 +5341,14 @@
         <v>140</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="H119" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-4.29</v>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D120" t="n">
         <v>177</v>
@@ -5383,10 +5383,10 @@
         <v>192</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>10.34</v>
+        <v>11.63</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>1.72</v>
+        <v>2.91</v>
       </c>
       <c r="H120" s="6" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="D121" t="n">
         <v>515</v>
@@ -5425,10 +5425,10 @@
         <v>519.86</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.98</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>0</v>
+        <v>-1.9</v>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="D123" t="n">
         <v>630</v>
@@ -5509,10 +5509,10 @@
         <v>650</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>12.07</v>
+        <v>13.04</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>8.619999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="H123" s="6" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
